--- a/SGC-CKN/Excel/245f5199-f15d-497d-aca6-8730fd6f3f55_Lô_CT-02_P7-89_D800_21-03-2026.xlsx
+++ b/SGC-CKN/Excel/245f5199-f15d-497d-aca6-8730fd6f3f55_Lô_CT-02_P7-89_D800_21-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="69">
   <si>
     <t>Dự án</t>
   </si>
@@ -190,9 +190,6 @@
   <si>
     <t xml:space="preserve">18:30
 21/03/2026</t>
-  </si>
-  <si>
-    <t>Độ sâu 41.3 được ghi chung cho các lớp cuối</t>
   </si>
   <si>
     <t>10</t>
@@ -1504,39 +1501,39 @@
         <v>8.4</v>
       </c>
       <c r="K19" s="31" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B20" s="33" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" s="35" t="s">
         <v>55</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F20" s="33">
         <v>-41.3</v>
       </c>
       <c r="G20" s="33">
-        <v>-41.3</v>
+        <v>-41.93</v>
       </c>
       <c r="H20" s="33">
         <v>0.17</v>
       </c>
       <c r="I20" s="33">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="J20" s="36">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="K20" s="34" t="s">
         <v>30</v>
@@ -1544,7 +1541,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1650,31 +1647,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1946,7 +1943,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D11" s="33">
         <v>1</v>
@@ -1955,21 +1952,21 @@
         <v>-41.3</v>
       </c>
       <c r="F11" s="33">
-        <v>-41.3</v>
+        <v>-41.93</v>
       </c>
       <c r="G11" s="33">
         <v>0.17</v>
       </c>
       <c r="H11" s="33">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="I11" s="36">
-        <v>0</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
@@ -1984,16 +1981,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="39">
-        <v>-41.3</v>
+        <v>-41.93</v>
       </c>
       <c r="G12" s="39">
         <v>3.25</v>
       </c>
       <c r="H12" s="39">
-        <v>41.3</v>
+        <v>41.93</v>
       </c>
       <c r="I12" s="39">
-        <v>12.71</v>
+        <v>12.9</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/245f5199-f15d-497d-aca6-8730fd6f3f55_Lô_CT-02_P7-89_D800_21-03-2026.xlsx
+++ b/SGC-CKN/Excel/245f5199-f15d-497d-aca6-8730fd6f3f55_Lô_CT-02_P7-89_D800_21-03-2026.xlsx
@@ -398,17 +398,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFBCFE8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF99F6E4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -593,26 +593,26 @@
     <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1454,88 +1454,88 @@
         <v>-37.1</v>
       </c>
       <c r="G18" s="27">
-        <v>-39.2</v>
+        <v>-38.2</v>
       </c>
       <c r="H18" s="27">
         <v>0.25</v>
       </c>
       <c r="I18" s="27">
-        <v>2.1</v>
-      </c>
-      <c r="J18" s="8">
-        <v>8.4</v>
+        <v>1.1</v>
+      </c>
+      <c r="J18" s="30">
+        <v>4.4</v>
       </c>
       <c r="K18" s="28" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="30">
-        <v>-39.2</v>
-      </c>
-      <c r="G19" s="30">
+      <c r="F19" s="31">
+        <v>-38.2</v>
+      </c>
+      <c r="G19" s="31">
         <v>-41.3</v>
       </c>
-      <c r="H19" s="30">
+      <c r="H19" s="31">
         <v>0.25</v>
       </c>
-      <c r="I19" s="30">
-        <v>2.1</v>
+      <c r="I19" s="31">
+        <v>3.1</v>
       </c>
       <c r="J19" s="8">
-        <v>8.4</v>
-      </c>
-      <c r="K19" s="31" t="s">
+        <v>12.4</v>
+      </c>
+      <c r="K19" s="32" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="33" t="s">
+      <c r="A20" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="35" t="s">
+      <c r="E20" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="34">
         <v>-41.3</v>
       </c>
-      <c r="G20" s="33">
+      <c r="G20" s="34">
         <v>-41.93</v>
       </c>
-      <c r="H20" s="33">
+      <c r="H20" s="34">
         <v>0.17</v>
       </c>
-      <c r="I20" s="33">
+      <c r="I20" s="34">
         <v>0.63</v>
       </c>
-      <c r="J20" s="36">
+      <c r="J20" s="30">
         <v>3.78</v>
       </c>
-      <c r="K20" s="34" t="s">
+      <c r="K20" s="35" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1894,73 +1894,73 @@
         <v>-37.1</v>
       </c>
       <c r="F9" s="27">
-        <v>-39.2</v>
+        <v>-38.2</v>
       </c>
       <c r="G9" s="27">
         <v>0.25</v>
       </c>
       <c r="H9" s="27">
-        <v>2.1</v>
-      </c>
-      <c r="I9" s="8">
-        <v>8.4</v>
+        <v>1.1</v>
+      </c>
+      <c r="I9" s="30">
+        <v>4.4</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="30">
+      <c r="A10" s="31">
         <v>9</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>1</v>
       </c>
-      <c r="E10" s="30">
-        <v>-39.2</v>
-      </c>
-      <c r="F10" s="30">
+      <c r="E10" s="31">
+        <v>-38.2</v>
+      </c>
+      <c r="F10" s="31">
         <v>-41.3</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="31">
         <v>0.25</v>
       </c>
-      <c r="H10" s="30">
-        <v>2.1</v>
+      <c r="H10" s="31">
+        <v>3.1</v>
       </c>
       <c r="I10" s="8">
-        <v>8.4</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="33">
+      <c r="A11" s="34">
         <v>10</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="34">
         <v>1</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="34">
         <v>-41.3</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="34">
         <v>-41.93</v>
       </c>
-      <c r="G11" s="33">
+      <c r="G11" s="34">
         <v>0.17</v>
       </c>
-      <c r="H11" s="33">
+      <c r="H11" s="34">
         <v>0.63</v>
       </c>
-      <c r="I11" s="36">
+      <c r="I11" s="30">
         <v>3.78</v>
       </c>
     </row>
